--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 09/01. Báo giá sửa chữa/BG_NguyenNam_290926.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 09/01. Báo giá sửa chữa/BG_NguyenNam_290926.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 09\01. Báo giá sửa chữa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F7E6C52-C9D3-49E7-9DCA-86B2AB47C470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA513768-1625-400B-92CA-F97007EE52D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
   <si>
     <t xml:space="preserve">STT </t>
   </si>
@@ -120,6 +120,12 @@
   </si>
   <si>
     <t>006080056238657</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>Đang chờ phản hồi lại báo giá</t>
   </si>
 </sst>
 </file>
@@ -441,6 +447,99 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="13"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="13"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -458,99 +557,6 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="13"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="13"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -933,97 +939,97 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="27"/>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="33" t="s">
+      <c r="A1" s="34"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="35"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="42"/>
     </row>
     <row r="2" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="36" t="s">
+      <c r="A2" s="34"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="38"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="45"/>
     </row>
     <row r="3" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="27"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="39" t="s">
+      <c r="A3" s="34"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="41"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="48"/>
     </row>
     <row r="4" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="30"/>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="42" t="s">
+      <c r="A4" s="37"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="44"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="51"/>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="23"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="54"/>
     </row>
     <row r="6" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
+      <c r="B6" s="57"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="8"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
-      <c r="J6" s="57" t="s">
+      <c r="J6" s="27" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="24"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -1033,11 +1039,11 @@
       <c r="J7" s="5"/>
     </row>
     <row r="8" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="24"/>
-      <c r="C8" s="24"/>
+      <c r="B8" s="55"/>
+      <c r="C8" s="55"/>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="14" t="s">
@@ -1050,11 +1056,11 @@
       <c r="AA8" s="2"/>
     </row>
     <row r="9" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
+      <c r="B9" s="56"/>
+      <c r="C9" s="56"/>
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
       <c r="F9" s="14"/>
@@ -1096,7 +1102,9 @@
       <c r="J10" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="K10" s="19"/>
+      <c r="K10" s="19" t="s">
+        <v>32</v>
+      </c>
       <c r="AA10" s="2"/>
     </row>
     <row r="11" spans="1:27" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1130,22 +1138,24 @@
       <c r="J11" s="12">
         <v>200000</v>
       </c>
-      <c r="K11" s="19"/>
+      <c r="K11" s="19" t="s">
+        <v>33</v>
+      </c>
       <c r="AA11" s="2"/>
     </row>
     <row r="12" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+      <c r="A12" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="47"/>
-      <c r="C12" s="47"/>
-      <c r="D12" s="47"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="47"/>
-      <c r="I12" s="48"/>
-      <c r="J12" s="49">
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="21">
         <f>SUM(J11:J11)</f>
         <v>200000</v>
       </c>
@@ -1166,42 +1176,42 @@
       <c r="AA13" s="2"/>
     </row>
     <row r="14" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="50" t="s">
+      <c r="A14" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="50" t="s">
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="H14" s="50"/>
-      <c r="I14" s="50"/>
-      <c r="J14" s="50"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
       <c r="AA14" s="2"/>
     </row>
     <row r="15" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="45" t="s">
+      <c r="A15" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="45"/>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
       <c r="F15" s="7"/>
-      <c r="G15" s="45" t="s">
+      <c r="G15" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="H15" s="45"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="45"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
       <c r="AA15" s="2"/>
     </row>
     <row r="16" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="52"/>
-      <c r="B16" s="52"/>
+      <c r="A16" s="23"/>
+      <c r="B16" s="23"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
@@ -1213,8 +1223,8 @@
       <c r="AA16" s="2"/>
     </row>
     <row r="17" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="53"/>
-      <c r="B17" s="53"/>
+      <c r="A17" s="24"/>
+      <c r="B17" s="24"/>
       <c r="C17" s="14"/>
       <c r="D17" s="14"/>
       <c r="E17" s="14"/>
@@ -1228,8 +1238,8 @@
       <c r="AA17" s="2"/>
     </row>
     <row r="18" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="53"/>
-      <c r="B18" s="53"/>
+      <c r="A18" s="24"/>
+      <c r="B18" s="24"/>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
@@ -1241,8 +1251,8 @@
       <c r="AA18" s="2"/>
     </row>
     <row r="19" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="53"/>
-      <c r="B19" s="53"/>
+      <c r="A19" s="24"/>
+      <c r="B19" s="24"/>
       <c r="C19" s="14"/>
       <c r="D19" s="14"/>
       <c r="E19" s="14"/>
@@ -1254,20 +1264,20 @@
       <c r="AA19" s="2"/>
     </row>
     <row r="20" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="54" t="s">
+      <c r="A20" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="B20" s="54"/>
-      <c r="C20" s="54"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="55"/>
-      <c r="G20" s="54" t="s">
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="H20" s="54"/>
-      <c r="I20" s="54"/>
-      <c r="J20" s="54"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33"/>
       <c r="K20" s="6"/>
       <c r="AA20" s="2"/>
     </row>
@@ -1278,10 +1288,10 @@
       <c r="D21" s="14"/>
       <c r="E21" s="14"/>
       <c r="F21" s="14"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="56"/>
-      <c r="I21" s="56"/>
-      <c r="J21" s="56"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="26"/>
+      <c r="J21" s="26"/>
       <c r="AA21" s="2"/>
     </row>
     <row r="22" spans="1:27" ht="17.25" x14ac:dyDescent="0.3">
@@ -1345,6 +1355,16 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="17">
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A1:D4"/>
+    <mergeCell ref="E1:J1"/>
+    <mergeCell ref="E2:J2"/>
+    <mergeCell ref="E3:J3"/>
+    <mergeCell ref="E4:J4"/>
     <mergeCell ref="A12:I12"/>
     <mergeCell ref="G14:J14"/>
     <mergeCell ref="G15:J15"/>
@@ -1352,16 +1372,6 @@
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A1:D4"/>
-    <mergeCell ref="E1:J1"/>
-    <mergeCell ref="E2:J2"/>
-    <mergeCell ref="E3:J3"/>
-    <mergeCell ref="E4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" display="http://vnetgps.vn" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
